--- a/report_forms/043_report_antisemitism_incident--report_forms.xlsx
+++ b/report_forms/043_report_antisemitism_incident--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'mr'}</t>
+          <t>mr</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Mr'}</t>
+          <t>Mr</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'ms'}</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Ms'}</t>
+          <t>Ms</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'bullying'}</t>
+          <t>bullying</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Bullying'}</t>
+          <t>Bullying</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'harassment'}</t>
+          <t>harassment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Harassment'}</t>
+          <t>Harassment</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'intimidation'}</t>
+          <t>intimidation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Intimidation'}</t>
+          <t>Intimidation</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'school'}</t>
+          <t>school</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'School'}</t>
+          <t>School</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'workplace'}</t>
+          <t>workplace</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Workplace'}</t>
+          <t>Workplace</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'organization'}</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Organization'}</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
